--- a/data/raw/Component_Category_COMC_554__Windows.xlsx
+++ b/data/raw/Component_Category_COMC_554__Windows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S7NM\Desktop\EOSL\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF748D13-CD5D-4B45-BC2F-6711531190E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3E733A-01DA-4D45-940A-7EC9EE782B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="825" activeTab="4" xr2:uid="{256E2C74-0424-4548-BE1E-F47234AD9C9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="825" activeTab="2" xr2:uid="{256E2C74-0424-4548-BE1E-F47234AD9C9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -7231,7 +7231,7 @@
       <c r="F2" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="3" t="s">
         <v>1244</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -25290,7 +25290,11 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="b06c99b3-cd83-43e5-b4c1-d62f316c1e37" ContentTypeId="0x01" PreviousValue="false"/>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25311,11 +25315,7 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="b06c99b3-cd83-43e5-b4c1-d62f316c1e37" ContentTypeId="0x01" PreviousValue="false"/>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25599,9 +25599,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A02480E-850D-43A5-9D68-F3DDA1C3C59F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186EEDBB-207D-4642-8886-FF19D9E1E9A4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25625,9 +25625,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186EEDBB-207D-4642-8886-FF19D9E1E9A4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A02480E-850D-43A5-9D68-F3DDA1C3C59F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
